--- a/instrumento-evaluacion-infografia.xlsx
+++ b/instrumento-evaluacion-infografia.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CF337D6-6100-496C-BDBF-58AC57333BF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11328" yWindow="0" windowWidth="11712" windowHeight="12240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>

--- a/instrumento-evaluacion-infografia.xlsx
+++ b/instrumento-evaluacion-infografia.xlsx
@@ -1,31 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitEducastur\CDD-ENDES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CF337D6-6100-496C-BDBF-58AC57333BF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{731E6429-8F8A-467D-9B8D-62D6372957F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11328" yWindow="0" windowWidth="11712" windowHeight="12240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>Instrumento de evaluación de la infografía interactiva</t>
   </si>
@@ -72,9 +83,6 @@
     <t>0 = no cumple</t>
   </si>
   <si>
-    <t>Alumno/a</t>
-  </si>
-  <si>
     <t>CE4.a: identifica la refactorización y un patrón</t>
   </si>
   <si>
@@ -103,6 +111,24 @@
   </si>
   <si>
     <t>Observaciones</t>
+  </si>
+  <si>
+    <t>Calificacion final (base 10)</t>
+  </si>
+  <si>
+    <t>Sergio, Mateo, Alonso</t>
+  </si>
+  <si>
+    <t>Mario, Enol</t>
+  </si>
+  <si>
+    <t>Alumnos/as</t>
+  </si>
+  <si>
+    <t>No se identifica un patron concreto</t>
+  </si>
+  <si>
+    <t>No explica la utilidad del analisis</t>
   </si>
 </sst>
 </file>
@@ -147,7 +173,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -170,11 +196,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -183,6 +220,10 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -463,139 +504,182 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="24.33203125" customWidth="1"/>
     <col min="2" max="2" width="19.21875" customWidth="1"/>
     <col min="3" max="3" width="22.21875" customWidth="1"/>
     <col min="4" max="4" width="24.6640625" customWidth="1"/>
     <col min="5" max="5" width="15.6640625" customWidth="1"/>
-    <col min="6" max="6" width="13.21875" customWidth="1"/>
+    <col min="6" max="6" width="25.21875" customWidth="1"/>
+    <col min="7" max="7" width="22.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="E12" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="F12" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="G12" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E13" s="2">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G13" s="5">
+        <f>SUM(B13:E13)/4*10</f>
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="2">
+        <v>1</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D14" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E14" s="2">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" s="5">
+        <f>SUM(B14:E14)/4*10</f>
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G15" s="5"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G16" s="5"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G17" s="5"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G18" s="5"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G19" s="5"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
+      <c r="G20" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
